--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512460_ELIMINGRA14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512460_ELIMINGRA14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5279</v>
+        <v>6.0529</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6928</v>
+        <v>7.346</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1649</v>
+        <v>-1.2931</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4265</v>
+        <v>2.4508</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8005</v>
+        <v>-0.7651</v>
       </c>
       <c r="I2" t="n">
-        <v>3.227</v>
+        <v>3.2159</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5068</v>
+        <v>3.673</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4926</v>
+        <v>-0.3796</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9994</v>
+        <v>4.0526</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0803</v>
+        <v>-1.2222</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7725</v>
+        <v>-0.8368</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3813</v>
+        <v>0.901</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2669</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1143</v>
+        <v>0.2291</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9191</v>
+        <v>3.0011</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9947</v>
+        <v>1.4012</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8199</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1748</v>
+        <v>1.9672</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.5838</v>
+        <v>-3.4778</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8727</v>
+        <v>-2.7662</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7111</v>
+        <v>-0.7116</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.039</v>
+        <v>-2.7938</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5648</v>
+        <v>-2.3808</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4742</v>
+        <v>-0.413</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5448</v>
+        <v>-0.6841</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1778</v>
+        <v>2.5422</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5992</v>
+        <v>1.9483</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5787</v>
+        <v>0.5939</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0118</v>
+        <v>0.6662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3421</v>
+        <v>1.2577</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3303</v>
+        <v>-0.5915</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1287</v>
+        <v>0.8288</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08</v>
+        <v>-1.2434</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0488</v>
+        <v>2.0722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3999</v>
+        <v>2.4918</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3199</v>
+        <v>-0.5567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08</v>
+        <v>3.0485</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5286</v>
+        <v>-1.663</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3999</v>
+        <v>-0.6867</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1287</v>
+        <v>-0.9762</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4001</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8947</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4001</v>
+        <v>2.921</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0578</v>
+        <v>0.9322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.058</v>
+        <v>-0.018</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.1032</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7284</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0742</v>
+        <v>0.2175</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7453</v>
+        <v>0.5184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6711</v>
+        <v>-0.3009</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1002</v>
+        <v>-0.1405</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.831</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2692</v>
+        <v>-0.0584</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.914</v>
+        <v>0.4095</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.638</v>
+        <v>0.3284</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.276</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1862</v>
+        <v>-0.55</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.193</v>
+        <v>-0.4105</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0069</v>
+        <v>-0.1395</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6265</v>
+        <v>0.248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.1089</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6572</v>
+        <v>0.1391</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1998</v>
+        <v>-0.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3334</v>
+        <v>-0.3702</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0911</v>
+        <v>0.1913</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4245</v>
+        <v>-0.5615</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2269</v>
+        <v>0.214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2069</v>
+        <v>0.1934</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2192</v>
+        <v>0.2543</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0711</v>
+        <v>0.1707</v>
       </c>
       <c r="U6" t="n">
-        <v>0.148</v>
+        <v>0.0835</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5588</v>
+        <v>-1.1151</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7543</v>
+        <v>-1.4634</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1954</v>
+        <v>0.3483</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2801</v>
+        <v>-2.0951</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9797</v>
+        <v>-0.8405</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3004</v>
+        <v>-1.2545</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.9282</v>
+        <v>-1.8714</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6141</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3141</v>
+        <v>-1.248</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6481</v>
+        <v>-0.2236</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6344</v>
+        <v>-0.2171</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0137</v>
+        <v>-0.0066</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2608</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9145</v>
+        <v>0.1606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3464</v>
+        <v>0.3772</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1398</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7829</v>
+        <v>-1.4391</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.599</v>
+        <v>-3.2825</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1839</v>
+        <v>1.8434</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759</v>
+        <v>-1.4306</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1927</v>
+        <v>0.0682</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9517</v>
+        <v>-1.4988</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2185</v>
+        <v>0.0271</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6344</v>
+        <v>0.6826</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8529</v>
+        <v>-0.6555</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4595</v>
+        <v>-1.4577</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5583</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9012</v>
+        <v>-0.8433</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0009</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.381</v>
+        <v>0.7773</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4555</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0745</v>
+        <v>0.1922</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1606</v>
+        <v>0.3826</v>
       </c>
       <c r="W8" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.439</v>
+        <v>-1.5153</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2903</v>
+        <v>-2.5175</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7293</v>
+        <v>1.0022</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007</v>
+        <v>-5.652</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9597</v>
+        <v>-3.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9667</v>
+        <v>-2.5382</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3216</v>
+        <v>-5.1929</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0382</v>
+        <v>-2.5349</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3598</v>
+        <v>-2.658</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3146</v>
+        <v>-0.4591</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9215</v>
+        <v>-0.5789</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3931</v>
+        <v>0.1198</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1864</v>
+        <v>1.2215</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3691</v>
+        <v>1.1749</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5555</v>
+        <v>0.0466</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4596</v>
+        <v>1.5521</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5999</v>
+        <v>1.5005</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0594</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4308</v>
+        <v>-1.5523</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4353</v>
+        <v>1.2434</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0045</v>
+        <v>-2.7956</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6695</v>
+        <v>-0.0192</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1068</v>
+        <v>-0.9853</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5627</v>
+        <v>0.9661</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.304</v>
+        <v>1.3702</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.592</v>
+        <v>-0.0077</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.712</v>
+        <v>1.3779</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3654</v>
+        <v>-1.3894</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5147</v>
+        <v>-0.9776</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1493</v>
+        <v>-0.4118</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4004</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2984</v>
+        <v>-0.2273</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4092</v>
+        <v>0.2363</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1108</v>
+        <v>-0.4635</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5399</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4596</v>
+        <v>0.6105</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0803</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4809</v>
+        <v>-1.7357</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8782</v>
+        <v>-1.6241</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3973</v>
+        <v>-0.1116</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4808</v>
+        <v>-2.283</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1094</v>
+        <v>-1.0058</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5903</v>
+        <v>-1.2772</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2212</v>
+        <v>-2.8265</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6034</v>
+        <v>-1.5625</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8247</v>
+        <v>-1.264</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2596</v>
+        <v>0.5436</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.494</v>
+        <v>0.5567</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.0131</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.0011</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8008</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2202</v>
+        <v>2.1257</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6558</v>
+        <v>1.8966</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4357</v>
+        <v>0.2291</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4204</v>
+        <v>-2.1626</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4204</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4029</v>
+        <v>-5.8003</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8281</v>
+        <v>-4.2261</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5748</v>
+        <v>-1.5742</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7693</v>
+        <v>-3.758</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8338</v>
+        <v>-2.8146</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9355</v>
+        <v>-0.9434</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.39</v>
+        <v>-3.3225</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3793</v>
+        <v>-0.4355</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.974</v>
+        <v>-0.347</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4378</v>
+        <v>0.0702</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5362</v>
+        <v>-0.4172</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.968500000000001</v>
+        <v>-5.190200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.004</v>
+        <v>-3.1228</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0354000000000001</v>
+        <v>-2.067299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.593</v>
+        <v>-15.3626</v>
       </c>
       <c r="H13" t="n">
-        <v>-13.4562</v>
+        <v>-13.4675</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.137</v>
+        <v>-1.894999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.329599999999999</v>
+        <v>-8.015000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.3428</v>
+        <v>-9.6722</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0131</v>
+        <v>1.657100000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.2633</v>
+        <v>-7.347600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.1133</v>
+        <v>-3.795499999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.15</v>
+        <v>-3.5521</v>
       </c>
       <c r="P13" t="n">
-        <v>4.0012</v>
+        <v>3.8948</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.0034</v>
+        <v>-11.6842</v>
       </c>
       <c r="R13" t="n">
-        <v>16.0046</v>
+        <v>15.5788</v>
       </c>
       <c r="S13" t="n">
-        <v>7.202599999999999</v>
+        <v>8.947700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.9924</v>
+        <v>7.955800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2103</v>
+        <v>0.992</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.5791</v>
+        <v>-2.6699</v>
       </c>
       <c r="W13" t="n">
-        <v>8.337</v>
+        <v>8.620600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.916</v>
+        <v>-11.2906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8999</v>
+        <v>4.6063</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2693</v>
+        <v>1.7954</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6306</v>
+        <v>2.8109</v>
       </c>
       <c r="G14" t="n">
-        <v>3.899</v>
+        <v>2.0617</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5154</v>
+        <v>1.1832</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3836</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6028</v>
+        <v>0.2247</v>
       </c>
       <c r="K14" t="n">
-        <v>2.203</v>
+        <v>0.1437</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3998</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2962</v>
+        <v>1.837</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3124</v>
+        <v>1.0396</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0162</v>
+        <v>0.7974</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1407</v>
+        <v>0.0704</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2873</v>
+        <v>0.0702</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8534</v>
+        <v>0.0002</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5399</v>
+        <v>1.5005</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4204</v>
+        <v>1.5005</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2446</v>
+        <v>3.6121</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6717</v>
+        <v>1.3254</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5729</v>
+        <v>2.2867</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1797</v>
+        <v>1.2111</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7187</v>
+        <v>-0.6496</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8984</v>
+        <v>1.8606</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.845</v>
+        <v>-0.6418</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.1667</v>
+        <v>-2.0036</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3217</v>
+        <v>1.3618</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0247</v>
+        <v>1.8529</v>
       </c>
       <c r="N15" t="n">
-        <v>1.448</v>
+        <v>1.3541</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5767</v>
+        <v>0.4988</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0055</v>
+        <v>-0.71</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3381</v>
+        <v>-0.3396</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3326</v>
+        <v>-0.3704</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="W15" t="n">
-        <v>3.1789</v>
+        <v>3.2805</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9463</v>
+        <v>3.153</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4351</v>
+        <v>2.3841</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5112</v>
+        <v>0.7689</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1322</v>
+        <v>3.8355</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2386</v>
+        <v>3.5459</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.2896</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2199</v>
+        <v>3.7431</v>
       </c>
       <c r="K16" t="n">
-        <v>0.14</v>
+        <v>2.3247</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08</v>
+        <v>1.4184</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9122</v>
+        <v>0.0924</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0986</v>
+        <v>1.2212</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8136</v>
+        <v>-1.1288</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6458</v>
+        <v>0.4801</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2445</v>
+        <v>0.192</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4013</v>
+        <v>0.2881</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4596</v>
+        <v>-1.5521</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4596</v>
+        <v>-0.3826</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9791</v>
+        <v>2.2715</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3532</v>
+        <v>1.0898</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6259</v>
+        <v>1.1817</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2319</v>
+        <v>3.1901</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8915</v>
+        <v>1.8724</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3404</v>
+        <v>1.3177</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1197</v>
+        <v>1.1479</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9997</v>
+        <v>1.0263</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1122</v>
+        <v>2.0422</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8918</v>
+        <v>0.8461</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2204</v>
+        <v>1.1961</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5935</v>
+        <v>-0.197</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2335</v>
+        <v>-0.0581</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.827</v>
+        <v>-0.1389</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7996</v>
+        <v>1.9975</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7996</v>
+        <v>1.1017</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.8959</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7996</v>
+        <v>-0.5666</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1997</v>
+        <v>-1.6477</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5999</v>
+        <v>1.0811</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7996</v>
+        <v>-0.859</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1997</v>
+        <v>-2.7965</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5999</v>
+        <v>1.9375</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.2924</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.1488</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0443</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.6486</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0071</v>
+        <v>1.8395</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6055</v>
+        <v>1.8395</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4016</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5667</v>
+        <v>1.8395</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6603</v>
+        <v>1.2316</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0936</v>
+        <v>0.6079</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0629</v>
+        <v>1.8395</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.9083</v>
+        <v>1.2316</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8454</v>
+        <v>0.6079</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4962</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2481</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7519</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0006</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2006</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6265</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.191</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4355</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0594</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3357</v>
+        <v>0.4605</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3357</v>
+        <v>0.4605</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1996,31 +1996,31 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4068</v>
+        <v>-0.2658</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4068</v>
+        <v>-0.2658</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.2797</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.2044</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.4841</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4068</v>
+        <v>2.024</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4068</v>
+        <v>2.0192</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.3305</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.306</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0244</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4068</v>
+        <v>0.6935</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4068</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.0197</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-3.5053</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.8947</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4068</v>
+        <v>-0.4017</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.3618</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4068</v>
+        <v>-0.0399</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.1626</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0483</v>
+        <v>0.1329</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4785</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4302</v>
+        <v>0.1329</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0201</v>
+        <v>0.3987</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9976</v>
+        <v>0.3987</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0225</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2434</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2415</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0019</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.3987</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7562</v>
+        <v>0.3987</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0206</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.601</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0011</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6071</v>
+        <v>-0.2658</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3801</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.227</v>
+        <v>-0.2658</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1398</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6593</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8148</v>
+        <v>-0.594</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1966</v>
+        <v>-2.0006</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3818</v>
+        <v>1.4066</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7742</v>
+        <v>0.7156</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3916</v>
+        <v>1.3593</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6437</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6162</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0218</v>
+        <v>0.0539</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3904</v>
+        <v>1.2857</v>
       </c>
       <c r="N23" t="n">
-        <v>1.3698</v>
+        <v>1.3054</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1889</v>
+        <v>-0.9202</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.4568</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6088</v>
+        <v>-0.4633</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2158</v>
+        <v>-0.7288</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5018</v>
+        <v>0.163</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.714</v>
+        <v>-0.8918</v>
       </c>
       <c r="G24" t="n">
-        <v>2.4062</v>
+        <v>2.4519</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4462</v>
+        <v>2.4924</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.04</v>
+        <v>-0.0405</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6087</v>
+        <v>2.7938</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1612</v>
+        <v>2.2502</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4476</v>
+        <v>0.5436</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2025</v>
+        <v>-0.3419</v>
       </c>
       <c r="N24" t="n">
-        <v>0.285</v>
+        <v>0.2422</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4875</v>
+        <v>-0.5841</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.001</v>
+        <v>-0.656</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.3535</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.312</v>
+        <v>-0.3025</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1245</v>
+        <v>-3.5075</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7903</v>
+        <v>-1.1558</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3342</v>
+        <v>-2.3517</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7955</v>
+        <v>-0.8003</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5068</v>
+        <v>0.5013</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3023</v>
+        <v>-1.3016</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5836</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1162</v>
+        <v>-0.0727</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3791</v>
+        <v>-1.446</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1861</v>
+        <v>-1.2289</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7288</v>
+        <v>-0.123</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1733</v>
+        <v>0.3406</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5555</v>
+        <v>-0.4635</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.0403</v>
+        <v>-3.8196</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2025</v>
+        <v>-4.2707</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1622</v>
+        <v>0.4511</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4366</v>
+        <v>-1.5302</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8343</v>
+        <v>0.7619</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.2709</v>
+        <v>-2.2921</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.3902</v>
+        <v>-2.3067</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4781</v>
+        <v>-0.4592</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.9121</v>
+        <v>-1.8475</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9536</v>
+        <v>0.7766</v>
       </c>
       <c r="N26" t="n">
-        <v>1.3124</v>
+        <v>1.2212</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3588</v>
+        <v>-0.4446</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1436</v>
+        <v>-0.8415</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8112</v>
+        <v>-0.0692</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3324</v>
+        <v>-0.7723</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.968599999999993</v>
+        <v>9.703099999999997</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.03530000000000122</v>
+        <v>2.0674</v>
       </c>
       <c r="F27" t="n">
-        <v>7.003899999999999</v>
+        <v>7.635800000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>15.5933</v>
+        <v>15.3626</v>
       </c>
       <c r="H27" t="n">
-        <v>13.4563</v>
+        <v>13.4673</v>
       </c>
       <c r="I27" t="n">
-        <v>2.137</v>
+        <v>1.8952</v>
       </c>
       <c r="J27" t="n">
-        <v>6.263400000000001</v>
+        <v>7.347600000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>3.113599999999999</v>
+        <v>3.7955</v>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>3.552099999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>9.329799999999999</v>
+        <v>8.015099999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>10.3429</v>
+        <v>9.6721</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.013</v>
+        <v>-1.657</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.001000000000001</v>
+        <v>-3.8948</v>
       </c>
       <c r="Q27" t="n">
-        <v>-16.0045</v>
+        <v>-15.5789</v>
       </c>
       <c r="R27" t="n">
-        <v>12.0035</v>
+        <v>11.6842</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.202599999999999</v>
+        <v>-4.4348</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.2103</v>
+        <v>-0.9918999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.9923</v>
+        <v>-3.4427</v>
       </c>
       <c r="V27" t="n">
-        <v>2.579</v>
+        <v>2.67</v>
       </c>
       <c r="W27" t="n">
-        <v>10.916</v>
+        <v>11.2906</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.337199999999999</v>
+        <v>-8.620699999999999</v>
       </c>
     </row>
   </sheetData>
